--- a/input/PL/DoFilesTargets/alignment_targets_employment.xlsx
+++ b/input/PL/DoFilesTargets/alignment_targets_employment.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="80" uniqueCount="32">
   <si>
     <t>year</t>
   </si>
@@ -105,6 +105,18 @@
   <si>
     <t>29 Mar 2026</t>
   </si>
+  <si>
+    <t>BUs with at least one responsible adult (demAge &gt;= 18) in a recognised group</t>
+  </si>
+  <si>
+    <t>Age 16-75, not student (labC4 != 2), not retired (labC4 != 4), not disabled (healthDsblLongtermFlag != 1)</t>
+  </si>
+  <si>
+    <t>BU-level weight = sum of person weights (wgtCrossMainSurvey) within the BU</t>
+  </si>
+  <si>
+    <t>28 Apr 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -114,7 +126,735 @@
     <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="183">
+  <fonts count="365">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -856,7 +1596,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="183">
+  <borders count="365">
     <border>
       <left/>
       <right/>
@@ -2138,11 +2878,1285 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="365">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -2869,6 +4883,734 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="182" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="183" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="184" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="185" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="186" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="187" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="188" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="189" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="190" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="191" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="192" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="193" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="194" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="195" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="196" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="197" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="198" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="199" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="200" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="201" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="202" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="203" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="204" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="205" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="206" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="207" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="208" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="209" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="210" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="211" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="212" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="213" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="214" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="215" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="216" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="217" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="218" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="219" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="220" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="221" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="222" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="223" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="224" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="225" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="226" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="227" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="228" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="229" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="230" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="231" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="232" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="233" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="234" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="235" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="236" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="237" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="238" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="239" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="240" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="241" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="242" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="243" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="244" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="245" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="246" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="247" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="248" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="249" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="250" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="251" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="252" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="253" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="254" fillId="0" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="255" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="256" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="257" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="258" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="259" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="260" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="261" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="262" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="263" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="264" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="265" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="266" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="267" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="268" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="269" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="270" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="271" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="272" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="273" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="274" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="275" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="276" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="277" fillId="0" borderId="277" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="278" fillId="0" borderId="278" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="279" fillId="0" borderId="279" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="280" fillId="0" borderId="280" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="281" fillId="0" borderId="281" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="282" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="283" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="284" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="285" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="286" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="287" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="288" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="289" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="290" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="291" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="292" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="293" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="294" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="295" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="296" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="297" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="298" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="299" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="300" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="301" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="302" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="303" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="304" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="305" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="306" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="307" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="308" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="309" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="310" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="311" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="312" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="313" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="314" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="315" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="316" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="317" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="318" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="319" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="320" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="321" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="322" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="323" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="324" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="325" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="326" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="327" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="328" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="329" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="330" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="331" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="332" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="333" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="334" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="335" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="336" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="337" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="338" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="339" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="340" fillId="0" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="341" fillId="0" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="342" fillId="0" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="343" fillId="0" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="344" fillId="0" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="345" fillId="0" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="346" fillId="0" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="347" fillId="0" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="348" fillId="0" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="349" fillId="0" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="350" fillId="0" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="351" fillId="0" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="352" fillId="0" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="353" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="354" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="355" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="356" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="357" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="358" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="359" fillId="0" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="360" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="361" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="362" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="363" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="364" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2893,106 +5635,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
+      <c r="A2" s="183">
         <v>2011</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="196">
         <v>0.81922071426119969</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="184">
         <v>2012</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="197">
         <v>0.81824475841038802</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3">
+      <c r="A4" s="185">
         <v>2013</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="198">
         <v>0.81275402503506544</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4">
+      <c r="A5" s="186">
         <v>2014</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="199">
         <v>0.82777375319856572</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="187">
         <v>2015</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="200">
         <v>0.82957299723645961</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="188">
         <v>2016</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="201">
         <v>0.83610776266089537</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7">
+      <c r="A8" s="189">
         <v>2017</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="202">
         <v>0.83775970878810269</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8">
+      <c r="A9" s="190">
         <v>2018</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="203">
         <v>0.84284034668221564</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9">
+      <c r="A10" s="191">
         <v>2019</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="204">
         <v>0.8485838971605224</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10">
+      <c r="A11" s="192">
         <v>2020</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="205">
         <v>0.86192143510533026</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11">
+      <c r="A12" s="193">
         <v>2021</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="206">
         <v>0.87709740463495611</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12">
+      <c r="A13" s="194">
         <v>2022</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="207">
         <v>0.87583630091615761</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="195">
         <v>2023</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="208">
         <v>0.88958048127895573</v>
       </c>
     </row>
@@ -3014,106 +5756,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="27">
+      <c r="A2" s="209">
         <v>2011</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B2" s="222">
         <v>0.39991491811397584</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28">
+      <c r="A3" s="210">
         <v>2012</v>
       </c>
-      <c r="B3" s="41">
+      <c r="B3" s="223">
         <v>0.41941850253143032</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29">
+      <c r="A4" s="211">
         <v>2013</v>
       </c>
-      <c r="B4" s="42">
+      <c r="B4" s="224">
         <v>0.39149701597436476</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="212">
         <v>2014</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="225">
         <v>0.41409816905821395</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="31">
+      <c r="A6" s="213">
         <v>2015</v>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="226">
         <v>0.41063698323768222</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32">
+      <c r="A7" s="214">
         <v>2016</v>
       </c>
-      <c r="B7" s="45">
+      <c r="B7" s="227">
         <v>0.42602830955555737</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33">
+      <c r="A8" s="215">
         <v>2017</v>
       </c>
-      <c r="B8" s="46">
+      <c r="B8" s="228">
         <v>0.45780746662740285</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="34">
+      <c r="A9" s="216">
         <v>2018</v>
       </c>
-      <c r="B9" s="47">
+      <c r="B9" s="229">
         <v>0.43430261801103048</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35">
+      <c r="A10" s="217">
         <v>2019</v>
       </c>
-      <c r="B10" s="48">
+      <c r="B10" s="230">
         <v>0.43507510852753173</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="36">
+      <c r="A11" s="218">
         <v>2020</v>
       </c>
-      <c r="B11" s="49">
-        <v>0.48013938494920982</v>
+      <c r="B11" s="231">
+        <v>0.48013938494920983</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37">
+      <c r="A12" s="219">
         <v>2021</v>
       </c>
-      <c r="B12" s="50">
+      <c r="B12" s="232">
         <v>0.45209736812057549</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="38">
+      <c r="A13" s="220">
         <v>2022</v>
       </c>
-      <c r="B13" s="51">
+      <c r="B13" s="233">
         <v>0.43644259131027485</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39">
+      <c r="A14" s="221">
         <v>2023</v>
       </c>
-      <c r="B14" s="52">
+      <c r="B14" s="234">
         <v>0.43754152493375359</v>
       </c>
     </row>
@@ -3135,106 +5877,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="53">
+      <c r="A2" s="235">
         <v>2011</v>
       </c>
-      <c r="B2" s="66">
+      <c r="B2" s="248">
         <v>0.53767479105636518</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="54">
+      <c r="A3" s="236">
         <v>2012</v>
       </c>
-      <c r="B3" s="67">
+      <c r="B3" s="249">
         <v>0.53923294433557334</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="55">
+      <c r="A4" s="237">
         <v>2013</v>
       </c>
-      <c r="B4" s="68">
+      <c r="B4" s="250">
         <v>0.52990487600433989</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="56">
+      <c r="A5" s="238">
         <v>2014</v>
       </c>
-      <c r="B5" s="69">
+      <c r="B5" s="251">
         <v>0.54121731627979208</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="57">
+      <c r="A6" s="239">
         <v>2015</v>
       </c>
-      <c r="B6" s="70">
+      <c r="B6" s="252">
         <v>0.55715966083459356</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="58">
+      <c r="A7" s="240">
         <v>2016</v>
       </c>
-      <c r="B7" s="71">
+      <c r="B7" s="253">
         <v>0.60925960659711664</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="59">
+      <c r="A8" s="241">
         <v>2017</v>
       </c>
-      <c r="B8" s="72">
+      <c r="B8" s="254">
         <v>0.61604743797977823</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="60">
+      <c r="A9" s="242">
         <v>2018</v>
       </c>
-      <c r="B9" s="73">
+      <c r="B9" s="255">
         <v>0.59203981548111762</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61">
+      <c r="A10" s="243">
         <v>2019</v>
       </c>
-      <c r="B10" s="74">
+      <c r="B10" s="256">
         <v>0.58483544528679632</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="62">
+      <c r="A11" s="244">
         <v>2020</v>
       </c>
-      <c r="B11" s="75">
+      <c r="B11" s="257">
         <v>0.58872002330024054</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="63">
+      <c r="A12" s="245">
         <v>2021</v>
       </c>
-      <c r="B12" s="76">
+      <c r="B12" s="258">
         <v>0.62659080700703695</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="64">
+      <c r="A13" s="246">
         <v>2022</v>
       </c>
-      <c r="B13" s="77">
+      <c r="B13" s="259">
         <v>0.61270480262528315</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="65">
+      <c r="A14" s="247">
         <v>2023</v>
       </c>
-      <c r="B14" s="78">
+      <c r="B14" s="260">
         <v>0.60256521207575575</v>
       </c>
     </row>
@@ -3256,106 +5998,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="79">
+      <c r="A2" s="261">
         <v>2011</v>
       </c>
-      <c r="B2" s="92">
+      <c r="B2" s="274">
         <v>0.30947190349703857</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="80">
+      <c r="A3" s="262">
         <v>2012</v>
       </c>
-      <c r="B3" s="93">
+      <c r="B3" s="275">
         <v>0.29999142781707649</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="81">
+      <c r="A4" s="263">
         <v>2013</v>
       </c>
-      <c r="B4" s="94">
+      <c r="B4" s="276">
         <v>0.30513882264282116</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="82">
+      <c r="A5" s="264">
         <v>2014</v>
       </c>
-      <c r="B5" s="95">
+      <c r="B5" s="277">
         <v>0.27889478378506316</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="83">
+      <c r="A6" s="265">
         <v>2015</v>
       </c>
-      <c r="B6" s="96">
+      <c r="B6" s="278">
         <v>0.27447434465403864</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="84">
+      <c r="A7" s="266">
         <v>2016</v>
       </c>
-      <c r="B7" s="97">
+      <c r="B7" s="279">
         <v>0.3010628200842741</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="85">
+      <c r="A8" s="267">
         <v>2017</v>
       </c>
-      <c r="B8" s="98">
+      <c r="B8" s="280">
         <v>0.30057456127581583</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="86">
+      <c r="A9" s="268">
         <v>2018</v>
       </c>
-      <c r="B9" s="99">
+      <c r="B9" s="281">
         <v>0.3068155386648328</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="87">
+      <c r="A10" s="269">
         <v>2019</v>
       </c>
-      <c r="B10" s="100">
+      <c r="B10" s="282">
         <v>0.35911211251470115</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="88">
+      <c r="A11" s="270">
         <v>2020</v>
       </c>
-      <c r="B11" s="101">
+      <c r="B11" s="283">
         <v>0.34448007649878137</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="89">
+      <c r="A12" s="271">
         <v>2021</v>
       </c>
-      <c r="B12" s="102">
+      <c r="B12" s="284">
         <v>0.35895948770059627</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="90">
+      <c r="A13" s="272">
         <v>2022</v>
       </c>
-      <c r="B13" s="103">
+      <c r="B13" s="285">
         <v>0.35891959698901466</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="91">
+      <c r="A14" s="273">
         <v>2023</v>
       </c>
-      <c r="B14" s="104">
+      <c r="B14" s="286">
         <v>0.36162281212755143</v>
       </c>
     </row>
@@ -3377,106 +6119,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="105">
+      <c r="A2" s="287">
         <v>2011</v>
       </c>
-      <c r="B2" s="118">
+      <c r="B2" s="300">
         <v>0.41637792579756672</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="106">
+      <c r="A3" s="288">
         <v>2012</v>
       </c>
-      <c r="B3" s="119">
-        <v>0.40012065055175255</v>
+      <c r="B3" s="301">
+        <v>0.40012065055175256</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="107">
+      <c r="A4" s="289">
         <v>2013</v>
       </c>
-      <c r="B4" s="120">
+      <c r="B4" s="302">
         <v>0.3904161588049252</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="108">
+      <c r="A5" s="290">
         <v>2014</v>
       </c>
-      <c r="B5" s="121">
+      <c r="B5" s="303">
         <v>0.39427163484472022</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="109">
+      <c r="A6" s="291">
         <v>2015</v>
       </c>
-      <c r="B6" s="122">
+      <c r="B6" s="304">
         <v>0.40683651449478769</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="110">
+      <c r="A7" s="292">
         <v>2016</v>
       </c>
-      <c r="B7" s="123">
+      <c r="B7" s="305">
         <v>0.4023565808905325</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="111">
+      <c r="A8" s="293">
         <v>2017</v>
       </c>
-      <c r="B8" s="124">
+      <c r="B8" s="306">
         <v>0.41094618970646801</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="112">
+      <c r="A9" s="294">
         <v>2018</v>
       </c>
-      <c r="B9" s="125">
+      <c r="B9" s="307">
         <v>0.42120975350176271</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="113">
+      <c r="A10" s="295">
         <v>2019</v>
       </c>
-      <c r="B10" s="126">
+      <c r="B10" s="308">
         <v>0.42573558591756905</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="114">
+      <c r="A11" s="296">
         <v>2020</v>
       </c>
-      <c r="B11" s="127">
+      <c r="B11" s="309">
         <v>0.40892825601147326</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="115">
+      <c r="A12" s="297">
         <v>2021</v>
       </c>
-      <c r="B12" s="128">
+      <c r="B12" s="310">
         <v>0.43199836014063375</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="116">
+      <c r="A13" s="298">
         <v>2022</v>
       </c>
-      <c r="B13" s="129">
+      <c r="B13" s="311">
         <v>0.43793085708406215</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="117">
+      <c r="A14" s="299">
         <v>2023</v>
       </c>
-      <c r="B14" s="130">
+      <c r="B14" s="312">
         <v>0.45836103599229056</v>
       </c>
     </row>
@@ -3498,106 +6240,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="131">
+      <c r="A2" s="313">
         <v>2011</v>
       </c>
-      <c r="B2" s="144">
+      <c r="B2" s="326">
         <v>0.29933200897339651</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="132">
+      <c r="A3" s="314">
         <v>2012</v>
       </c>
-      <c r="B3" s="145">
+      <c r="B3" s="327">
         <v>0.30176454671587055</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="133">
+      <c r="A4" s="315">
         <v>2013</v>
       </c>
-      <c r="B4" s="146">
+      <c r="B4" s="328">
         <v>0.3016004516529307</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="134">
+      <c r="A5" s="316">
         <v>2014</v>
       </c>
-      <c r="B5" s="147">
+      <c r="B5" s="329">
         <v>0.30996615307239028</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="135">
+      <c r="A6" s="317">
         <v>2015</v>
       </c>
-      <c r="B6" s="148">
+      <c r="B6" s="330">
         <v>0.30969260372255614</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="136">
+      <c r="A7" s="318">
         <v>2016</v>
       </c>
-      <c r="B7" s="149">
+      <c r="B7" s="331">
         <v>0.31142571283334575</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="137">
+      <c r="A8" s="319">
         <v>2017</v>
       </c>
-      <c r="B8" s="150">
+      <c r="B8" s="332">
         <v>0.30857087190915561</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="138">
+      <c r="A9" s="320">
         <v>2018</v>
       </c>
-      <c r="B9" s="151">
+      <c r="B9" s="333">
         <v>0.30045978659290212</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="139">
+      <c r="A10" s="321">
         <v>2019</v>
       </c>
-      <c r="B10" s="152">
+      <c r="B10" s="334">
         <v>0.31149821531271515</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="140">
+      <c r="A11" s="322">
         <v>2020</v>
       </c>
-      <c r="B11" s="153">
+      <c r="B11" s="335">
         <v>0.31156186771356276</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="141">
+      <c r="A12" s="323">
         <v>2021</v>
       </c>
-      <c r="B12" s="154">
+      <c r="B12" s="336">
         <v>0.31841282100364365</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="142">
+      <c r="A13" s="324">
         <v>2022</v>
       </c>
-      <c r="B13" s="155">
+      <c r="B13" s="337">
         <v>0.34230606345172992</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="143">
+      <c r="A14" s="325">
         <v>2023</v>
       </c>
-      <c r="B14" s="156">
+      <c r="B14" s="338">
         <v>0.33895780142077747</v>
       </c>
     </row>
@@ -3619,106 +6361,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="157">
+      <c r="A2" s="339">
         <v>2011</v>
       </c>
-      <c r="B2" s="170">
+      <c r="B2" s="352">
         <v>0.44847245270758812</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="158">
+      <c r="A3" s="340">
         <v>2012</v>
       </c>
-      <c r="B3" s="171">
+      <c r="B3" s="353">
         <v>0.44273290541849708</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="159">
+      <c r="A4" s="341">
         <v>2013</v>
       </c>
-      <c r="B4" s="172">
+      <c r="B4" s="354">
         <v>0.44590869368365277</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="160">
+      <c r="A5" s="342">
         <v>2014</v>
       </c>
-      <c r="B5" s="173">
+      <c r="B5" s="355">
         <v>0.45383332938325444</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="161">
+      <c r="A6" s="343">
         <v>2015</v>
       </c>
-      <c r="B6" s="174">
+      <c r="B6" s="356">
         <v>0.47500210104953605</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="162">
+      <c r="A7" s="344">
         <v>2016</v>
       </c>
-      <c r="B7" s="175">
-        <v>0.46944343431379359</v>
+      <c r="B7" s="357">
+        <v>0.4694434343137936</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="163">
+      <c r="A8" s="345">
         <v>2017</v>
       </c>
-      <c r="B8" s="176">
+      <c r="B8" s="358">
         <v>0.48081258688981376</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="164">
+      <c r="A9" s="346">
         <v>2018</v>
       </c>
-      <c r="B9" s="177">
+      <c r="B9" s="359">
         <v>0.48708268402268529</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="165">
+      <c r="A10" s="347">
         <v>2019</v>
       </c>
-      <c r="B10" s="178">
+      <c r="B10" s="360">
         <v>0.48737889167035214</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="166">
+      <c r="A11" s="348">
         <v>2020</v>
       </c>
-      <c r="B11" s="179">
+      <c r="B11" s="361">
         <v>0.50012717105501536</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="167">
+      <c r="A12" s="349">
         <v>2021</v>
       </c>
-      <c r="B12" s="180">
+      <c r="B12" s="362">
         <v>0.52691709065005843</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="168">
+      <c r="A13" s="350">
         <v>2022</v>
       </c>
-      <c r="B13" s="181">
+      <c r="B13" s="363">
         <v>0.53300950855579898</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="169">
+      <c r="A14" s="351">
         <v>2023</v>
       </c>
-      <c r="B14" s="182">
+      <c r="B14" s="364">
         <v>0.51857369593384961</v>
       </c>
     </row>
@@ -3752,7 +6494,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -3768,7 +6510,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -3784,7 +6526,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -3832,7 +6574,7 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
